--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -6438,11 +6438,11 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (32414) ; À SUPPRIMER (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (614) ; À SUPPRIMER (TESTS) (412) ; À SUPPRIMER (DOUBLON AZ) (278) ; INCONNU (158) ; À SUPPRIMER (DOUBLON S3-AZ) (157)</t>
+          <t>TRANSFERT_S3_OK (32414) ; À SUPPRIMER (DIFFUSION) (12229) ; À SUPPRIMER (TESTS) (412) ; EN LIGNE - À TRANSFERER ? (366) ; À SUPPRIMER (DOUBLON AZ) (278) ; À SUPPRIMER (DIFFUSION - MASTER DÉJÀ SUR S3) (248) ; INCONNU (158) ; À SUPPRIMER (DOUBLON S3-AZ) (157)</t>
         </is>
       </c>
       <c r="M78" s="6" t="n">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="N78" s="4" t="n">
         <v>33024</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (2191648) ; À SUPPRIMER (DIFFUSION) (131832) ; INCONNU (29156) ; À SUPPRIMER (REMPLACEMENT) (20276) ; À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (12654) ; À TRANSFERER (8156) ; À SUPPRIMER (DOUBLON) (7616) ; À SUPPRIMER (DOUBLON S3-AZ) (6179) ; À SUPPRIMER (DOUBLON AZ) (5914) ; EN LIGNE - À TRANSFERER ? (5020) ; À CHERCHER (4682) ; À SUPPRIMER (FILE_TYPE) (2329) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (MED_PAR) (686) ; À TRANSFERER APRES VALIDATION (517) ; À SUPPRIMER (TESTS) (412) ; INCONNU FRAD59 (180) ; S3_KEY À CONSTRUIRE (54) ; DOUBLON - À VOIR (38) ; INCONNU VOIR MARIE (4) ; À TRANSFERER VOIR MARIE (1)</t>
+          <t>TRANSFERT_S3_OK (2191648) ; À SUPPRIMER (DIFFUSION) (131832) ; INCONNU (29156) ; À SUPPRIMER (REMPLACEMENT) (20276) ; À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (12654) ; À TRANSFERER (8156) ; À SUPPRIMER (DOUBLON) (7616) ; À SUPPRIMER (DOUBLON S3-AZ) (6179) ; À SUPPRIMER (DOUBLON AZ) (5914) ; EN LIGNE - À TRANSFERER ? (4772) ; À CHERCHER (4682) ; À SUPPRIMER (FILE_TYPE) (2329) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (MED_PAR) (686) ; À TRANSFERER APRES VALIDATION (517) ; À SUPPRIMER (TESTS) (412) ; À SUPPRIMER (DIFFUSION - MASTER DÉJÀ SUR S3) (248) ; INCONNU FRAD59 (180) ; S3_KEY À CONSTRUIRE (54) ; DOUBLON - À VOIR (38) ; INCONNU VOIR MARIE (4) ; À TRANSFERER VOIR MARIE (1)</t>
         </is>
       </c>
       <c r="M104" s="10" t="n">
